--- a/screenshot_ocr/screenshot_texts.xlsx
+++ b/screenshot_ocr/screenshot_texts.xlsx
@@ -1,215 +1,200 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26148" windowHeight="13740"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="26148" windowHeight="13740" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="截图文字记录" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="截图文字记录" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>序号</t>
-  </si>
-  <si>
-    <t>截图时间</t>
-  </si>
-  <si>
-    <t>提取的文字</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
-    <font>
+  <numFmts count="0"/>
+  <fonts count="24">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -515,161 +500,167 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -725,11 +716,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1016,39 +1070,815 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.6" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" ht="15" spans="1:3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-    </row>
-    <row r="3" ht="15" spans="1:3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
+    <row r="1" ht="15.6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>截图时间</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>提取的文字</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:42:19</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月15日19:44
+我现在手里拿了好多只股，有的是7月一直炒到现在的
+方桂斌
+2025年10月15日19:43
+我不一定有时间啊
+方桂斌
+2025年10月15日19:41
+我就是有觉的不错的，又有时间就分享下，但是上班忙可能
+就没了
+3
+方桂斌
+2025年10月15日19:40
+@一禅你要交费吗，保证我有月收入，我立刻辞职全职
+3
+方桂斌
+2025年10月15日19:38
+炒股有风险，我看好的也不一定涨，有可能我分享出来的某
+只股他就没涨，还跌到止损了，因为我买了十几只股，可能
+我其他股涨了，又觉得我藏着，我可以把我持仓的所有股都
+给你们知道，但是有些盘中没时间发出来的股，那没办法，
+毕竟股市变化快，我肯定是先优先我自己的持仓操作
+方桂斌
+2025年10月15日19:34
+有比较看好的某只股有时间的话我会发到这里，先事先声
+明，因为我自己买了很多只股，我自己也要操作，有时候并
+不一定有时间能通知道你们，大概止损位我会说明，但是止
+盈自己把控，还有做t也是自己把控，不做也行</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:42:57</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月15日19:4
+先拿一只股的半仓进
+S
+方桂斌
+2025年10月15日19:4
+和峰子
+3
+方桂斌
+2025年10月15日19:4
+今天分享了西藏珠峰和通富微电给健哥
+方桂斌
+2025年10月15日19:4
+所以我自己的持仓操作都不一定忙得过来</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:43:21</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月16日10:39
+@健哥仔通富微电，健哥零花钱到手了
+方桂斌
+2025年10月16日09:55
+大金重工
+方桂斌
+2025年10月16日09:48
+这个要耐心的中线
+方桂斌
+2025年10月16日09:47
+看着买
+方桂斌
+2025年10月16日09:47
+晋控煤业
+方桂斌
+2025年10月15日19:59
+今天回了一口血</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:43:53</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>3
+方桂斌
+2025年10月16日11:31
+你现在才卖吗我高点5个多点都卖了，现在果然回落了
+方桂斌
+2025年10月16日11:02
+我卖了一半
+方桂斌
+2025年10月16日11:01
+通富微电先出
+方桂斌
+2025年10月16日10:57
+这个低吸成功，这就是分时技术
+方桂斌
+2025年10月16日10:54
+亏损
+方桂斌
+2025年10月16日10:54
+因为你刚玩，我怕你承受不了
+方桂斌
+2025年10月16日10:53
+昨天没敢让你买满一只股的仓位
+S
+方桂斌
+2025年10月16日10:50
+大赚了，健哥是没起床吗，这就是大礼包的生活吗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:44:24</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月16日14:53
+有大金重工的可以不买金风科技
+方桂斌
+2025年10月16日14:53
+中电港、金风科技，搞点底仓
+方桂斌
+2025年10月16日14:20
+早上卖掉的通富微电，我考虑接回
+方桂斌
+2025年10月16日11:31
+说的时候还有5个多点</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:44:54</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月17日16:28
+@健哥仔完了，健哥刚进来就被大A教育了
+方桂斌
+2025年10月17日12:43
+昨晚凌晨三点特朗普讲了什么，今天股市跌成这样
+方桂斌
+2025年10月17日10:12
+特朗普那条微博，今天果然跌麻了
+3
+方桂斌
+2025年10月17日09:37
+西藏再涨注意减仓
+方桂斌
+2025年10月17日09:37
+北方稀土
+方桂斌
+2025年10月17日09:21
+我的华天复牌了
+方桂斌
+2025年10月17日09:12
+但是开口放人，一哥还不舍得走
+方桂斌
+2025年10月17日08:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:45:09</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月17日1
+破位的注意卖掉了，情况不对我也考虑降低仓位了</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:45:49</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>不过这个股是打算拿中长线的
+方桂斌
+2025年10月20日11:26
+是的，赚了就减减仓，尾盘再看接回
+方桂斌
+2025年10月20日11:24
+在等这周的会议落地
+方桂斌
+2025年10月20日11:23
+资金还是很慎重
+方桂斌
+2025年10月20日11:23
+涨了就减减仓，今天这里只能算是弱修复
+方桂斌
+2025年10月20日11:18
+这么说，健哥还赚了
+方桂斌
+2025年10月20日11:03
+也该轮到煤炭上场了
+方桂斌
+2025年10月20日11:02
+晋控煤业果然没看错
+3
+方桂斌
+2025年10月20日11:00
+健哥，通富微电回血了吧</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:46:25</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月20日11:31
+做T技术不好的，就尾盘快收盘再接回
+方桂斌
+2025年10月20日11:30
+现在减仓只是为了防止盈利回落</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:47:39</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月20日21:08
+今天缩量修复，场内资金竞价修复，场外资金观望，这并不
+是一件好事，今天开始只要任何一次修复不放量，都要减
+仓，只要一直是这样不放量轮动，我看大盘指数还可能会有
+一次新低杀跌
+方桂斌
+2025年10月20日15:33
+How zre you
+方桂斌
+2025年10月20日15:33
+坐稳扶好，别想把我甩下车
+方桂斌
+2025年10月20日15:00
+我是真没想到晋控煤业这么猛
+方桂斌
+2025年10月20日12:40
+今早这个股，天地板，再地天板，飞一样的感觉</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:48:35</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>关注会议的十五五计划等待中央的政策提示
+方桂斌
+2025年10月21日12:37
+我最近拿到的需求都是给S级英雄的特效给我做，也忙的要
+死，烦死了，这么多特效，尽是给大招我搞，我只想做小兵
+特效
+方桂斌
+2025年10月21日12:32
+0
+方桂斌
+2025年10月21日12:31
+@destiny峰子是前段时间回调被干沉默了吗
+方桂斌
+2025年10月21日12:30
+晋控我放着没动
+方桂斌
+2025年10月21日12:29
+下午开盘我准备开新股
+方桂斌
+2025年10月21日12:02
+今天终于放量了，嘎嘎回血，可以渐渐出手了
+方桂斌
+2025年10月21日10:28
+快乐的通富微电</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:48:55</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>3
+方桂斌
+2025年10月21日13:08
+光库科技，光迅科技，三花智控，找个合适的点进
+3
+方桂斌
+2025年10月21日12:54
+今天这个大盘只能算是止跌不是反转，仓位上控制下不要上
+头
+3
+方桂斌
+2025年10月21日12:42
+下一波主线应该就在这里产生</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:49:23</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>3
+方桂斌
+2025年10月21日13:38
+五洲可以的，我在这里面赚了不少
+方桂斌
+2025年10月21日13:31
+五洲新春也不错
+方桂斌
+2025年10月21日13:30
+这几个都可以</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:50:36</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>5
+方桂斌
+反复进进出出</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:50:52</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+@destiny这个做t技术有水平不</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:51:07</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+怎么才能害割逃菜割到我
+方桂斌
+做t成本线越做越低了</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:51:34</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月22日10:33
+我之前一直拿着的大金重工今天爽飞了，峰子哥
+方桂斌
+2025年10月22日10:32
+这个是今天新开仓的
+方桂斌
+2025年10月22日10:22
+昨天的三花，光迅，五洲都涨了
+方桂斌
+2025年10月22日10:20
+云南褚业，开仓
+6
+品房
+0201
+民堂元务号艺元房务学房质有
+品房
+全02521
+乖~
+你还年轻
+听我的
+0
+把你的钱给我
+你自己再去赚好不好
+方持斌
+2025年10月21日15:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:53:31</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>万桂斌
+先不加
+S
+方桂斌
+2025年10月22日10:40
+@健哥仔这个股，暂时看可以拿到过年
+方桂斌
+2025年10月22日10:38
+机会多的是，这次错过没上车，等下一次他回踩，你再上，
+不要盲目追高
+方桂斌
+2025年10月22日10:37
+不过你昨天没上今天追高不太合适@健哥仔
+S
+方桂斌
+2025年10月22日10:36
+抬高股价
+方桂斌
+2025年10月22日10:36
+三花这个股更容易吸引资金
+方桂斌
+2025年10月22日10:35
+而且三花的公司运营各个基本面都很好，市盈率估值还有很
+大预期
+方桂斌
+2025年10月22日10:34
+@健哥仔五洲和三花是同一概念题材，但是三花会比五洲更
+有识别度和代表性，特斯拉机器人领头羊</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:54:34</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月22日11:12
+中电港开新仓，明天如果涨了就减仓锁盈利
+S
+方桂斌
+2025年10月22日10:58
+现在看大盘不是很好，早上追高的，今天都要被割
+S
+方桂斌
+2025年10月22日10:58
+量能后继不足，今天又盈利的还没回落的先减仓
+3
+方桂斌
+2025年10月22日10:46
+@健哥仔涨了要减仓，其实你建仓，要吧资金分配好，只有
+一手减也不是，不减也不是
+3
+方桂斌
+2025年10月22日10:44
+除非大盘放巨量，指数共振每个版块一起大涨，缩量情况
+下，煤炭大涨，按理来说，大A个股要暴跌
+方桂斌
+2025年10月22日10:43
+一旦煤炭大涨，大多数是大A每个版块都大跌的时候
+方桂斌
+2025年10月22日10:43
+煤炭波动不大的，都是慢慢涨的
+方桂斌
+2025年10月22日10:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:55:14</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>今天的缅A又是股民受伤的一天
+方桂斌
+2025年10月22日13:25
+中电港，低吸吃爽了
+方桂斌
+2025年10月22日11:57
+这个10月股民都很难受，大部分人都是亏麻的状态，这个月
+确实不好做，能控制不大亏，这个月就是稳住
+方桂斌
+2025年10月22日11:55
+方桂斌
+2025年10月22日11:35
+方桂斌
+2025年10月22日11:35
+我在等一个大盘的放量
+方桂斌
+2025年10月22日11:13
+如果明天跌了，到今天的最低点还是有支撑，就再加仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:55:39</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月22日15:08
+7月到现在连赚三个月，不能这个月断了吧
+方桂斌
+2025年10月22日15:08
+看下周月底降息会不会来一次暴力反弹，搞不好我这个月还
+不会亏
+方桂斌
+2025年10月22日15:04
+看网评，这个月很多股民都把前几个月甚至这一年的盈利，
+一次性亏完了
+方桂斌
+2025年10月22日15:02
+股市想赚钱关键还是控制亏损
+方桂斌
+2025年10月22日15:01
+这个月还亏钱，不过是小亏</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:56:09</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月23日10:11
+光库科技高点出完货，收工
+方桂斌
+2025年10月23日10:04
+光库科技今天终于也嘎嘎涨了
+方桂斌
+2025年10月23日09:48
+云南褚业止损
+3
+方桂斌
+2025年10月23日09:36
+我刚加完
+方桂斌
+2025年10月23日09:36
+晋控煤业加仓了没
+方桂斌
+2025年10月22日20:50
+是啊，跌停开口翻红那天走的话，只是亏16%，不走现在起
+码亏40%
+方桂斌
+2025年10月22日20:01
+一哥不是说不走吗，亏了30%那会说不走了，现在还没走的定位到聊天位置
+话，应该亏40%几了
+方桂斌
+2025年10月22日19:13
+居然还有直播海南华铁索赔专场</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:56:46</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+加仓后，涨了又继续慢慢减仓，循环往复
+S
+方桂斌
+2025年10月23日10:41
+西藏珠峰我看可以慢慢加仓了
+6
+品育房
+全0235
+品局品局：有房务员—前学院
+房
+全0255
+@一禅这么多股，你看，实盘还是需要自己盯盘操作的，不
+是给一只股就能赚钱，什么时候涨了要卖，跌了要补，顺子
+是不是也在偷偷赚钱
+S
+方桂斌
+2025年10月23日10:17
+三花还是牛逼啊，这都红了
+方桂斌
+2025年10月23日10:16
+今早三花给了低吸上车或者加仓的机会
+3
+方桂斌
+2025年10月23日10:15
+目前在短期低位，再观察一两天
+方桂斌
+2025年10月23日10:1
+五洲连破2个支撑位，第3支撑位止住，再看看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:57:17</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>方桂斌
+2025年10月23日11:19
+ALL IN毁一生
+3
+方桂斌
+2025年10月23日11:19
+如果真的像他说的，海南华铁他基本全仓了，那确实要被干
+懵逼
+方桂斌
+2025年10月23日11:14
+他说退市都说了几百年了，都还一直在玩
+方桂斌
+2025年10月23日11:13
+@destiny你怎么知道，我觉得他是不会退市的
+方桂斌
+2025年10月23日11:13
+涨了就要卖一部分，留一部分
+方桂斌
+2025年10月23日11:12
+可以
+方桂斌
+2025年10月23日11:06
+像一哥这种性子，最近如果还在玩股市的话，应该亏的挺惨
+的
+方桂斌
+2025年10月23日11:03
+最近大A这种反复震荡的混沌期，很多散户玩着玩着，钱就定位到聊天位置</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>